--- a/tests/test_excelparser/onto_only_classes.xlsx
+++ b/tests/test_excelparser/onto_only_classes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\flb\projects\Team4.0\EMMOntoPy\tests\test_excelparser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\flb\projects\interoperability_tools\EMMOntoPy\tests\test_excelparser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE65BD73-2602-4B98-B53B-7411E0E084FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8712825C-395C-47BE-B7BE-82727132B1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-47745" yWindow="-6420" windowWidth="38700" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-48570" yWindow="-3450" windowWidth="34470" windowHeight="17640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -446,7 +446,7 @@
     <t>Object</t>
   </si>
   <si>
-    <t>https://w3id.org/emmo/inferred</t>
+    <t>https://raw.githubusercontent.com/emmo-repo/EMMOntoPy/refs/heads/master/tests/testonto/emmo/emmo-squashed.ttl</t>
   </si>
 </sst>
 </file>
@@ -554,9 +554,6 @@
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -597,6 +594,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1009,91 +1009,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="6"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4">
         <v>0.01</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1101,36 +1101,36 @@
       <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C12" s="4"/>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C13" s="4"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C14" s="4"/>
+      <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C15" s="4"/>
+      <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C16" s="10"/>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C17" s="10"/>
+      <c r="C17" s="9"/>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C18" s="10"/>
+      <c r="C18" s="9"/>
     </row>
     <row r="19" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C19" s="10"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C20" s="10"/>
+      <c r="C20" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1149,32 +1149,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>138</v>
       </c>
       <c r="B3" t="s">
@@ -1194,7 +1194,7 @@
       <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1204,9 +1204,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{A7FD5117-5D75-4961-B7FA-FB5F57D6DC02}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -1233,84 +1230,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="10" t="s">
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="9" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="9" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1357,16 +1354,16 @@
       <c r="A7" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>70</v>
       </c>
       <c r="G7" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="9"/>
+      <c r="H7" s="8"/>
       <c r="J7" t="s">
         <v>72</v>
       </c>
@@ -1378,13 +1375,13 @@
       <c r="B8" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>75</v>
       </c>
       <c r="G8" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="9"/>
+      <c r="H8" s="8"/>
       <c r="J8" t="s">
         <v>76</v>
       </c>
@@ -1393,7 +1390,7 @@
       <c r="A9" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>78</v>
       </c>
       <c r="E9" t="s">
@@ -1402,7 +1399,7 @@
       <c r="G9" t="s">
         <v>80</v>
       </c>
-      <c r="H9" s="9"/>
+      <c r="H9" s="8"/>
       <c r="J9" t="s">
         <v>81</v>
       </c>
@@ -1411,10 +1408,10 @@
       <c r="A10" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="8"/>
       <c r="E10" t="s">
         <v>84</v>
       </c>
@@ -1426,7 +1423,7 @@
       <c r="A11" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>86</v>
       </c>
       <c r="D11" t="s">
@@ -1443,7 +1440,7 @@
       <c r="A12" t="s">
         <v>89</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>75</v>
       </c>
       <c r="G12" t="s">
@@ -1457,7 +1454,7 @@
       <c r="A13" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>93</v>
       </c>
       <c r="E13" t="s">
@@ -1474,7 +1471,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C14" s="9"/>
+      <c r="C14" s="8"/>
       <c r="J14" t="s">
         <v>98</v>
       </c>
@@ -1483,7 +1480,7 @@
       <c r="A15" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>100</v>
       </c>
       <c r="E15" t="s">
@@ -1500,7 +1497,7 @@
       <c r="A16" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>75</v>
       </c>
       <c r="G16" t="s">
@@ -1514,7 +1511,7 @@
       <c r="A17" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>75</v>
       </c>
       <c r="G17" t="s">
@@ -1528,7 +1525,7 @@
       <c r="A18" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G18" t="s">
@@ -1542,7 +1539,7 @@
       <c r="A19" t="s">
         <v>110</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>75</v>
       </c>
       <c r="J19" t="s">
@@ -1591,14 +1588,14 @@
       <c r="A24" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="9"/>
+      <c r="D24" s="8"/>
       <c r="G24" t="s">
         <v>71</v>
       </c>
-      <c r="H24" s="9"/>
+      <c r="H24" s="8"/>
       <c r="J24" t="s">
         <v>120</v>
       </c>
